--- a/docs/Sprint 3/Team_building.xlsx
+++ b/docs/Sprint 3/Team_building.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sergi\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sergi\Desktop\ISPP-G8\ISPP-G8\docs\Sprint 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1A5807-F03A-4605-95FC-F9AF77F8460E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A28E20-F6B7-42D8-98C6-C8807736C350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1015,16 +1015,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>185737</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>609599</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>71437</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>9524</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1630,11 +1630,21 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.7"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="50"/>
+        <cfvo type="percent" val="80"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
@@ -1650,21 +1660,11 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percent" val="50"/>
-        <cfvo type="percent" val="80"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0.7"/>
-        <cfvo type="num" val="1"/>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
